--- a/final_data_pipeline/output/312120_elec_options.xlsx
+++ b/final_data_pipeline/output/312120_elec_options.xlsx
@@ -1772,7 +1772,7 @@
         <v>77</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AE12">
         <v>8000</v>
@@ -1867,7 +1867,7 @@
         <v>77</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AE13">
         <v>8000</v>
@@ -1965,7 +1965,7 @@
         <v>77</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AE14">
         <v>8000</v>
@@ -2063,7 +2063,7 @@
         <v>77</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AE15">
         <v>8000</v>
@@ -2158,7 +2158,7 @@
         <v>77</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AE16">
         <v>8000</v>
@@ -2253,7 +2253,7 @@
         <v>77</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AE17">
         <v>8000</v>
@@ -2348,7 +2348,7 @@
         <v>77</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AE18">
         <v>8000</v>
@@ -2443,7 +2443,7 @@
         <v>77</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AE19">
         <v>8000</v>
@@ -2538,7 +2538,7 @@
         <v>77</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AE20">
         <v>8000</v>
@@ -2633,7 +2633,7 @@
         <v>77</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>17.71296296296294</v>
       </c>
       <c r="AE21">
         <v>8000</v>
@@ -2731,7 +2731,7 @@
         <v>77</v>
       </c>
       <c r="AD22">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE22">
         <v>8000</v>
@@ -2826,7 +2826,7 @@
         <v>77</v>
       </c>
       <c r="AD23">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE23">
         <v>8000</v>
@@ -2921,7 +2921,7 @@
         <v>77</v>
       </c>
       <c r="AD24">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE24">
         <v>8000</v>
@@ -3016,7 +3016,7 @@
         <v>77</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE25">
         <v>8000</v>
@@ -3111,7 +3111,7 @@
         <v>77</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE26">
         <v>8000</v>
@@ -9420,7 +9420,7 @@
         <v>77</v>
       </c>
       <c r="AD92">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE92">
         <v>8000</v>
@@ -9515,7 +9515,7 @@
         <v>77</v>
       </c>
       <c r="AD93">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE93">
         <v>8000</v>
@@ -9610,7 +9610,7 @@
         <v>77</v>
       </c>
       <c r="AD94">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE94">
         <v>8000</v>
@@ -9705,7 +9705,7 @@
         <v>77</v>
       </c>
       <c r="AD95">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE95">
         <v>8000</v>
@@ -9803,7 +9803,7 @@
         <v>77</v>
       </c>
       <c r="AD96">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE96">
         <v>8000</v>
@@ -9898,7 +9898,7 @@
         <v>77</v>
       </c>
       <c r="AD97">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE97">
         <v>8000</v>
@@ -9993,7 +9993,7 @@
         <v>77</v>
       </c>
       <c r="AD98">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE98">
         <v>8000</v>
@@ -10088,7 +10088,7 @@
         <v>77</v>
       </c>
       <c r="AD99">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE99">
         <v>8000</v>
@@ -10186,7 +10186,7 @@
         <v>77</v>
       </c>
       <c r="AD100">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE100">
         <v>8000</v>
@@ -10281,7 +10281,7 @@
         <v>77</v>
       </c>
       <c r="AD101">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE101">
         <v>8000</v>
@@ -11332,7 +11332,7 @@
         <v>77</v>
       </c>
       <c r="AD112">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE112">
         <v>8000</v>
@@ -11427,7 +11427,7 @@
         <v>77</v>
       </c>
       <c r="AD113">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE113">
         <v>8000</v>
@@ -11522,7 +11522,7 @@
         <v>77</v>
       </c>
       <c r="AD114">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE114">
         <v>8000</v>
@@ -11617,7 +11617,7 @@
         <v>77</v>
       </c>
       <c r="AD115">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE115">
         <v>8000</v>
@@ -11715,7 +11715,7 @@
         <v>77</v>
       </c>
       <c r="AD116">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE116">
         <v>8000</v>
@@ -11810,7 +11810,7 @@
         <v>77</v>
       </c>
       <c r="AD117">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE117">
         <v>8000</v>
@@ -11905,7 +11905,7 @@
         <v>77</v>
       </c>
       <c r="AD118">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE118">
         <v>8000</v>
@@ -12000,7 +12000,7 @@
         <v>77</v>
       </c>
       <c r="AD119">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE119">
         <v>8000</v>
@@ -12098,7 +12098,7 @@
         <v>77</v>
       </c>
       <c r="AD120">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE120">
         <v>8000</v>
@@ -12196,7 +12196,7 @@
         <v>77</v>
       </c>
       <c r="AD121">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE121">
         <v>8000</v>
@@ -12291,7 +12291,7 @@
         <v>77</v>
       </c>
       <c r="AD122">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE122">
         <v>8000</v>
@@ -12386,7 +12386,7 @@
         <v>77</v>
       </c>
       <c r="AD123">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE123">
         <v>8000</v>
@@ -12481,7 +12481,7 @@
         <v>77</v>
       </c>
       <c r="AD124">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE124">
         <v>8000</v>
@@ -12576,7 +12576,7 @@
         <v>77</v>
       </c>
       <c r="AD125">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE125">
         <v>8000</v>
@@ -12671,7 +12671,7 @@
         <v>77</v>
       </c>
       <c r="AD126">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE126">
         <v>8000</v>
@@ -15156,7 +15156,7 @@
         <v>77</v>
       </c>
       <c r="AD152">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE152">
         <v>8000</v>
@@ -15251,7 +15251,7 @@
         <v>77</v>
       </c>
       <c r="AD153">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE153">
         <v>8000</v>
@@ -15346,7 +15346,7 @@
         <v>77</v>
       </c>
       <c r="AD154">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE154">
         <v>8000</v>
@@ -15441,7 +15441,7 @@
         <v>77</v>
       </c>
       <c r="AD155">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE155">
         <v>8000</v>
@@ -15539,7 +15539,7 @@
         <v>77</v>
       </c>
       <c r="AD156">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE156">
         <v>8000</v>
@@ -15634,7 +15634,7 @@
         <v>77</v>
       </c>
       <c r="AD157">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE157">
         <v>8000</v>
@@ -15729,7 +15729,7 @@
         <v>77</v>
       </c>
       <c r="AD158">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE158">
         <v>8000</v>
@@ -15824,7 +15824,7 @@
         <v>77</v>
       </c>
       <c r="AD159">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE159">
         <v>8000</v>
@@ -15919,7 +15919,7 @@
         <v>77</v>
       </c>
       <c r="AD160">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE160">
         <v>8000</v>
@@ -16017,7 +16017,7 @@
         <v>77</v>
       </c>
       <c r="AD161">
-        <v>10</v>
+        <v>-1.819444444444444</v>
       </c>
       <c r="AE161">
         <v>8000</v>
